--- a/reporting/descriptive-sample-output/descriptive-revenue-bridge.xlsx
+++ b/reporting/descriptive-sample-output/descriptive-revenue-bridge.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descriptive Review" sheetId="1" r:id="R5625055560eb456f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bridge Calculation" sheetId="2" r:id="R4b37bf1d15ba4f26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definition Appendix" sheetId="3" r:id="R99b90a33222e4468"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Inputs" sheetId="4" r:id="Rad58ff491660416f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descriptive Review" sheetId="1" r:id="R02c9411d8d7945bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bridge Calculation" sheetId="2" r:id="R34f771a5c92d457d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definition Appendix" sheetId="3" r:id="Rb34f69665eab4a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Inputs" sheetId="4" r:id="R1ba03aa5f90c46be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -393,7 +393,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R58deb198a9d64f3e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10c85d774a47480b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -403,9 +403,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -455,7 +455,7 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -928,7 +928,7 @@
     <x:mergeCell ref="C29:N29"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racbc611806fc4d12"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebc924ad74a64348"/>
 </x:worksheet>
 </file>
 
